--- a/Assets/Resources/Configs/EquipmentConfig.xlsx
+++ b/Assets/Resources/Configs/EquipmentConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProgram\SoulFighterSurvivor\Assets\Resources\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C78E532-EC89-4EAC-9CCE-2BD5F1958A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908AAA34-DA1C-4B04-92D1-A51F8B7346E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="25845" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="394">
   <si>
     <t>id</t>
   </si>
@@ -59,21 +59,6 @@
     <t>AttributeAnvil</t>
   </si>
   <si>
-    <t>LegendaryFighterEquipmentAnvil</t>
-  </si>
-  <si>
-    <t>LegendaryShooterEquipmentAnvil</t>
-  </si>
-  <si>
-    <t>LegendaryAssassinEquipmentAnvil</t>
-  </si>
-  <si>
-    <t>LegendaryTankEquipmentAnvil</t>
-  </si>
-  <si>
-    <t>PrismaticEquipmentAnvil</t>
-  </si>
-  <si>
     <t>InfinityEdge</t>
   </si>
   <si>
@@ -191,12 +176,6 @@
     <t>传说级法师装备</t>
   </si>
   <si>
-    <t>传说级坦克装备</t>
-  </si>
-  <si>
-    <t>棱彩装备</t>
-  </si>
-  <si>
     <t>无尽之刃</t>
   </si>
   <si>
@@ -510,9 +489,6 @@
   </si>
   <si>
     <t>自动开启一个半随机的选择，以选取一件传说级法师装备。</t>
-  </si>
-  <si>
-    <t>自动开启一个半随机的选择，以选取一件传说级坦克装备。</t>
   </si>
   <si>
     <t>每6秒获得1层充能，至多6层，技能命中会消耗所有充能来对目标造成&lt;color=#C97BFF&gt;{0:F0}&lt;/color&gt;=（80+&lt;color=#C97BFF&gt;5%&lt;/color&gt;&lt;sprite="Attributes" name="AbilityPowerIcon"&gt;+&lt;color=#FF8A00&gt;6%额外&lt;/color&gt;&lt;sprite="Attributes" name="AttackDamageIcon"&gt;）×（0.65+0.35×充能层数）的魔法伤害。</t>
@@ -716,25 +692,12 @@
     <t>Shooter</t>
   </si>
   <si>
-    <t>Tank</t>
-  </si>
-  <si>
-    <t>Fighter,Wizard,Tank,Assassin,Shooter</t>
-  </si>
-  <si>
     <t>Shooter</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Assassin</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tank</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wizard,Tank</t>
   </si>
   <si>
     <t>Fighter,Assassin,Shooter</t>
@@ -1034,10 +997,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>自动开启一个半随机的选择，以选取一件棱彩级装备装备。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>NavoriQuickblades</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1062,26 +1021,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>RapidFirecannon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>疾射火炮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>远程消耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"attackSpeed":0.30,"criticalRate":0.25,"percentageMovementSpeed":0.04}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>神射手</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Stormrazor</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1219,10 +1158,6 @@
   </si>
   <si>
     <t>CursedBlade</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你的盈能攻击造成&lt;color=#00D8FF&gt;200魔法伤害&lt;/color&gt;并在完全盈能时获得35%攻击距离。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1405,6 +1340,67 @@
   </si>
   <si>
     <t>施放技能后5秒内，下次攻击会附带额外的&lt;color=#00D8FF&gt;{0:F0}&lt;/color&gt;=（&lt;color=#FF6161&gt;75%基础&lt;sprite="Attributes" name="AttackDamageIcon"&gt;&lt;/color&gt;+&lt;color=#C97BFF&gt;66%&lt;sprite="Attributes" name="AbilityPowerIcon"&gt;&lt;/color&gt;）魔法伤害的攻击特效。冷却时间3秒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BlackCleavers</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑色切割者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"attackDamage": 40, "maxHealthPoint": 350, "abilityHaste": 20}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对英雄造成&lt;color=#FF6A6A&gt;物理伤害&lt;/color&gt;时会施加6%&lt;sprite="Attributes" name="AttackDefenseIcon"&gt;削减，持续6秒，至多叠至30%&lt;sprite="Attributes" name="AttackDefenseIcon"&gt;削减。
+造成&lt;color=#FF6A6A&gt;物理伤害&lt;/color&gt;时会提供持续2秒的20&lt;sprite="Attributes" name="MovementSpeedIcon"&gt;。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>狂怒切割</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SunderedSky</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>焚天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持续作战</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"attackDamage": 40, "maxHealthPoint": 350, "abilityHaste": 10}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你对一个英雄打出的第一次攻击会暴击，并回复自身&lt;color=#0ACD02&gt;{0:F0}&lt;/color&gt; =（&lt;color=#FF6161&gt;150%基础&lt;sprite="Attributes" name="AttackDamageIcon"&gt;&lt;/color&gt;）外加&lt;color=#0ACD02&gt;6%已损失&lt;sprite="Attributes" name="MaxHealthPointIcon"&gt;&lt;/color&gt;。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>光盾打击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fighter,Wizard,Assassin,Shooter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LegendaryFighterEquipmentAnvil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LegendaryShooterEquipmentAnvil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LegendaryAssassinEquipmentAnvil</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1754,14 +1750,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BO14"/>
+  <dimension ref="A1:BN14"/>
   <sheetFormatPr defaultColWidth="32.375" defaultRowHeight="18.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="24" width="32.375" style="1"/>
     <col min="26" max="16384" width="32.375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:66" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1786,766 +1782,760 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="P1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AK1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AM1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AN1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO1" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="AP1" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="AQ1" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="AR1" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="M1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI1" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="AK1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="AL1" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM1" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AN1" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO1" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP1" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="AQ1" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="AR1" s="5" t="s">
-        <v>253</v>
-      </c>
       <c r="AS1" s="5" t="s">
-        <v>256</v>
+        <v>223</v>
       </c>
       <c r="AT1" s="5" t="s">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="AU1" s="5" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="AV1" s="5" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="AW1" s="5" t="s">
         <v>262</v>
       </c>
       <c r="AX1" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AY1" s="5" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AZ1" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="BA1" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
+      </c>
+      <c r="BA1" s="3" t="s">
+        <v>379</v>
       </c>
       <c r="BB1" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="BC1" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="BC1" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="BD1" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="BD1" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="BE1" s="5" t="s">
+      <c r="BE1" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="BF1" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BG1" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="BH1" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="BF1" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="BG1" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="BH1" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="BI1" s="3" t="s">
-        <v>342</v>
+      <c r="BI1" s="5" t="s">
+        <v>340</v>
       </c>
       <c r="BJ1" s="5" t="s">
         <v>345</v>
       </c>
       <c r="BK1" s="5" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="BL1" s="5" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="BM1" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="BN1" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="BO1" s="5" t="s">
-        <v>379</v>
+        <v>360</v>
+      </c>
+      <c r="BN1" s="3" t="s">
+        <v>384</v>
       </c>
     </row>
-    <row r="2" spans="1:67" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:66" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="J2" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="K2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="S2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="Z2" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="AA2" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="AB2" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="AC2" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="Y2" s="4" t="s">
+      <c r="AD2" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="Z2" s="4" t="s">
+      <c r="AE2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AA2" s="4" t="s">
+      <c r="AF2" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AB2" s="4" t="s">
+      <c r="AG2" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="AC2" s="4" t="s">
+      <c r="AH2" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="AD2" s="4" t="s">
+      <c r="AI2" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="AE2" s="4" t="s">
+      <c r="AJ2" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="AF2" s="4" t="s">
+      <c r="AK2" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="AG2" s="4" t="s">
+      <c r="AL2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="AH2" s="4" t="s">
+      <c r="AM2" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="AI2" s="4" t="s">
+      <c r="AN2" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="AJ2" s="4" t="s">
+      <c r="AO2" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AK2" s="4" t="s">
+      <c r="AP2" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="AQ2" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="AL2" s="4" t="s">
+      <c r="AR2" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="AM2" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AN2" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AO2" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AP2" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="AQ2" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="AR2" s="5" t="s">
+      <c r="AS2" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="AT2" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="AU2" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="AS2" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="AT2" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AU2" s="5" t="s">
-        <v>236</v>
-      </c>
       <c r="AV2" s="5" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="AW2" s="5" t="s">
         <v>263</v>
       </c>
       <c r="AX2" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AY2" s="5" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AZ2" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="BA2" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
+      </c>
+      <c r="BA2" s="3" t="s">
+        <v>380</v>
       </c>
       <c r="BB2" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="BC2" s="3" t="s">
-        <v>311</v>
+        <v>298</v>
+      </c>
+      <c r="BC2" s="5" t="s">
+        <v>302</v>
       </c>
       <c r="BD2" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="BE2" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="BF2" s="5" t="s">
-        <v>324</v>
+        <v>306</v>
+      </c>
+      <c r="BE2" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="BF2" s="3" t="s">
+        <v>317</v>
       </c>
       <c r="BG2" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="BH2" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="BI2" s="3" t="s">
-        <v>340</v>
+        <v>322</v>
+      </c>
+      <c r="BH2" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="BI2" s="5" t="s">
+        <v>342</v>
       </c>
       <c r="BJ2" s="5" t="s">
         <v>346</v>
       </c>
       <c r="BK2" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="BL2" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="BM2" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="BL2" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="BM2" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="BN2" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="BO2" s="5" t="s">
-        <v>380</v>
+      <c r="BN2" s="3" t="s">
+        <v>385</v>
       </c>
     </row>
-    <row r="3" spans="1:67" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:66" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="Q3" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="R3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="U3" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="Z3" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="AA3" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="AB3" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC3" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="T3" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="W3" s="1" t="s">
+      <c r="AD3" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="AE3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="AF3" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="AG3" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AB3" s="1" t="s">
+      <c r="AH3" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="AC3" s="1" t="s">
+      <c r="AI3" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="AD3" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE3" s="1" t="s">
+      <c r="AJ3" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="AF3" s="1" t="s">
+      <c r="AK3" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="AG3" s="1" t="s">
+      <c r="AL3" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="AH3" s="1" t="s">
+      <c r="AM3" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="AI3" s="1" t="s">
+      <c r="AN3" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="AJ3" s="1" t="s">
+      <c r="AO3" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="AK3" s="1" t="s">
+      <c r="AP3" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AL3" s="1" t="s">
+      <c r="AQ3" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="AM3" s="1" t="s">
+      <c r="AR3" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="AN3" s="1" t="s">
+      <c r="AS3" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="AT3" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="AU3" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="AV3" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="AW3" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="AX3" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="AY3" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="AZ3" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="BA3" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="BB3" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="BC3" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="BD3" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="BE3" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BF3" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="BG3" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="BH3" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="BI3" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="BJ3" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="BK3" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="BL3" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="BM3" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="BN3" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="4" spans="1:66" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="AO3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="AP3" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="AQ3" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="AR3" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AL4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AM4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AN4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AO4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AP4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AR4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AS4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AT4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AU4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AV4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AW4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AX4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AY4" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="AZ4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BA4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BB4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BC4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BD4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BE4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BF4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BG4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BH4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BI4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BJ4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BK4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BL4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BM4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BN4" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:66" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="AS3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AT3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AU3" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="AV3" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="AW3" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="AX3" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="AY3" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="AZ3" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="BA3" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="BB3" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="BC3" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="BD3" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="BE3" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="BF3" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="BG3" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="BH3" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="BI3" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="BJ3" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="BK3" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="BL3" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="BM3" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="BN3" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="BO3" s="3" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="4" spans="1:67" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AC4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AD4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AE4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AF4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AG4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AH4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AI4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AJ4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AK4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AN4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AO4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AP4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AQ4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AR4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AS4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AT4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AU4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AV4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AW4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AX4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AY4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AZ4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BA4" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="BB4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BC4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BD4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BE4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BF4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BG4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BH4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BI4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BJ4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BK4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BL4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BM4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BN4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BO4" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:67" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="B5" s="1">
         <v>500</v>
@@ -2581,10 +2571,10 @@
         <v>2000</v>
       </c>
       <c r="M5" s="1">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="N5" s="1">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="O5" s="1">
         <v>2500</v>
@@ -2695,13 +2685,13 @@
         <v>2500</v>
       </c>
       <c r="AY5" s="1">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="AZ5" s="1">
         <v>2500</v>
       </c>
       <c r="BA5" s="1">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="BB5" s="1">
         <v>2500</v>
@@ -2742,545 +2732,539 @@
       <c r="BN5" s="1">
         <v>2500</v>
       </c>
-      <c r="BO5" s="1">
-        <v>2500</v>
-      </c>
     </row>
-    <row r="6" spans="1:67" ht="273" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:66" ht="273" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="M6" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="N6" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="O6" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="P6" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="Q6" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="R6" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="S6" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="T6" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="U6" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="V6" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="Q6" s="1" t="s">
+      <c r="W6" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="R6" s="1" t="s">
+      <c r="X6" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="S6" s="1" t="s">
+      <c r="Y6" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="T6" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="U6" s="1" t="s">
+      <c r="Z6" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="AA6" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="AB6" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="V6" s="1" t="s">
+      <c r="AC6" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="W6" s="1" t="s">
+      <c r="AD6" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="X6" s="1" t="s">
+      <c r="AE6" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="AF6" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="AG6" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="Y6" s="1" t="s">
+      <c r="AH6" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AI6" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="Z6" s="1" t="s">
+      <c r="AJ6" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="AA6" s="1" t="s">
+      <c r="AK6" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="AB6" s="3" t="s">
+      <c r="AL6" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AM6" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN6" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AO6" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="AP6" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="AQ6" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AR6" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="AS6" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="AT6" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="AU6" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="AV6" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="AW6" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="AX6" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="AY6" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="AZ6" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="BA6" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="BB6" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="AC6" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="AD6" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="AE6" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="AF6" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="AG6" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="AH6" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="AI6" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="AJ6" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="AK6" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="AL6" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="AM6" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="AN6" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="AO6" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="AP6" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="AQ6" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="AR6" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="AS6" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="AT6" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="AU6" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="AV6" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="AW6" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="AX6" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="AY6" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="AZ6" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="BA6" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="BB6" s="3" t="s">
-        <v>307</v>
-      </c>
       <c r="BC6" s="3" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="BD6" s="3" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="BE6" s="3" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="BF6" s="3" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="BG6" s="3" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="BH6" s="3" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="BI6" s="3" t="s">
         <v>343</v>
       </c>
       <c r="BJ6" s="3" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="BK6" s="3" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="BL6" s="3" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
       <c r="BM6" s="3" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="BN6" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="BO6" s="3" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
-    <row r="7" spans="1:67" ht="270" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:66" ht="270" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="P7" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="H7" s="1" t="s">
+      <c r="Q7" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="R7" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="S7" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="T7" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="U7" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="V7" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="X7" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="V7" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="X7" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA7" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="AB7" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AD7" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="AF7" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="AI7" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AJ7" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="AK7" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="AL7" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="AM7" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="AB7" s="1" t="s">
+      <c r="AN7" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="AO7" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="AP7" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="AQ7" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="AR7" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="AS7" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="AT7" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="AU7" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="AV7" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="AW7" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="AX7" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="AY7" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="AZ7" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="BA7" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="BB7" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="BC7" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="BE7" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="BF7" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="BG7" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="BH7" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="BI7" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="BJ7" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="BK7" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="BL7" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="BM7" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="BN7" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="8" spans="1:66" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="AC7" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="AD7" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="AE7" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="AF7" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="AH7" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="AI7" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ7" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="AK7" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="AL7" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="AM7" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="AN7" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="AO7" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="AP7" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="AQ7" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="AR7" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="AS7" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="AT7" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="AU7" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="AV7" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="AW7" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="AX7" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="AY7" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="AZ7" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="BA7" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="BB7" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="BC7" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="BD7" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="BE7" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="BG7" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="BH7" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="BI7" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="BJ7" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="BK7" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="BL7" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="BM7" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="BN7" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="BO7" s="3" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="8" spans="1:67" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="V8" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="P8" s="1" t="s">
+      <c r="X8" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="W8" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="X8" s="1" t="s">
-        <v>185</v>
       </c>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="AF8" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="AG8" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="AH8" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="AB8" s="1" t="s">
+      <c r="AI8" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="AC8" s="1" t="s">
+      <c r="AJ8" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="AD8" s="1" t="s">
+      <c r="AK8" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="AE8" s="1" t="s">
+      <c r="AL8" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="AF8" s="1" t="s">
+      <c r="AM8" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="AH8" s="1" t="s">
+      <c r="AN8" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="AI8" s="1" t="s">
+      <c r="AO8" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="AJ8" s="1" t="s">
+      <c r="AP8" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="AK8" s="1" t="s">
+      <c r="AQ8" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="AL8" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="AM8" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="AN8" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="AO8" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="AP8" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="AQ8" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="AR8" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="AS8" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="AT8" s="3" t="s">
-        <v>234</v>
+      <c r="AR8" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="AS8" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="AT8" s="1" t="s">
+        <v>233</v>
       </c>
       <c r="AU8" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="AV8" s="1" t="s">
-        <v>245</v>
+        <v>255</v>
+      </c>
+      <c r="AV8" s="3" t="s">
+        <v>260</v>
       </c>
       <c r="AW8" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AX8" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AY8" s="3" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="AZ8" s="3" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="BA8" s="3" t="s">
-        <v>297</v>
+        <v>383</v>
       </c>
       <c r="BB8" s="3" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="BC8" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="BD8" s="3" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="BE8" s="3" t="s">
-        <v>323</v>
+        <v>315</v>
+      </c>
+      <c r="BF8" s="3" t="s">
+        <v>320</v>
       </c>
       <c r="BG8" s="3" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="BH8" s="3" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="BI8" s="3" t="s">
         <v>344</v>
       </c>
       <c r="BJ8" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="BK8" s="3" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="BL8" s="3" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="BM8" s="3" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="BN8" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="BO8" s="3" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
-    <row r="9" spans="1:67" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:66" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B9" s="1">
         <v>5</v>
@@ -3319,25 +3303,25 @@
         <v>0</v>
       </c>
       <c r="N9" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S9" s="1">
         <v>0</v>
       </c>
       <c r="T9" s="1">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="U9" s="1">
         <v>0</v>
@@ -3358,654 +3342,650 @@
         <v>0</v>
       </c>
       <c r="AA9" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB9" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="1">
+        <v>5</v>
+      </c>
+      <c r="AJ9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="1">
+        <v>5</v>
+      </c>
+      <c r="AW9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="1">
         <v>10</v>
       </c>
-      <c r="AD9" s="1">
-        <v>3</v>
-      </c>
-      <c r="AE9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="1">
+      <c r="AY9" s="1">
+        <v>30</v>
+      </c>
+      <c r="AZ9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE9" s="1">
         <v>5</v>
       </c>
-      <c r="AL9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AO9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AP9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AS9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AT9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AU9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AV9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AW9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AX9" s="1">
-        <v>5</v>
-      </c>
-      <c r="AY9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AZ9" s="1">
+      <c r="BF9" s="1">
         <v>10</v>
       </c>
-      <c r="BA9" s="1">
+      <c r="BG9" s="1">
         <v>30</v>
       </c>
-      <c r="BB9" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC9" s="1">
-        <v>0</v>
-      </c>
-      <c r="BD9" s="1">
-        <v>0</v>
-      </c>
-      <c r="BE9" s="1">
-        <v>0</v>
-      </c>
-      <c r="BF9" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG9" s="1">
-        <v>5</v>
-      </c>
       <c r="BH9" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="BI9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BM9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BN9" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:66" ht="270.60000000000002" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="Y10" s="1"/>
+      <c r="AD10"/>
+      <c r="AO10" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="AQ10" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="BK10" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="BL10" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="11" spans="1:66" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="Y11" s="1"/>
+      <c r="AD11"/>
+      <c r="AO11" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="AQ11" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="BK11" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="BL11" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="12" spans="1:66" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
+        <v>0</v>
+      </c>
+      <c r="T12" s="1">
+        <v>0</v>
+      </c>
+      <c r="U12" s="1">
+        <v>0</v>
+      </c>
+      <c r="V12" s="1">
+        <v>0</v>
+      </c>
+      <c r="W12" s="1">
+        <v>25</v>
+      </c>
+      <c r="X12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="1">
+        <v>20</v>
+      </c>
+      <c r="AP12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="1">
         <v>10</v>
       </c>
-      <c r="BI9" s="1">
-        <v>30</v>
-      </c>
-      <c r="BJ9" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="BK9" s="1">
-        <v>0</v>
-      </c>
-      <c r="BL9" s="1">
-        <v>0</v>
-      </c>
-      <c r="BM9" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN9" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO9" s="1">
+      <c r="AR12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK12" s="1">
+        <v>15</v>
+      </c>
+      <c r="BL12" s="1">
+        <v>10</v>
+      </c>
+      <c r="BM12" s="1">
+        <v>0</v>
+      </c>
+      <c r="BN12" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:67" ht="270.60000000000002" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="H10" s="1" t="s">
+    <row r="13" spans="1:66" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="Y10" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q13" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="AF10"/>
-      <c r="AQ10" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="AS10" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="BM10" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="BN10" s="3" t="s">
-        <v>396</v>
+      <c r="R13" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y13" s="1"/>
+      <c r="AB13" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="AD13"/>
+      <c r="AE13" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="AG13" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="AI13" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK13" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="AQ13" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="AY13" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="BA13" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="BD13" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="BH13" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="BI13" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="BK13" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="BL13" s="3" t="s">
+        <v>353</v>
       </c>
     </row>
-    <row r="11" spans="1:67" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="Y11" s="1" t="s">
+    <row r="14" spans="1:66" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="AF11"/>
-      <c r="AQ11" s="1" t="s">
+      <c r="B14" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="N14" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="AS11" s="1" t="s">
+      <c r="O14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="AA14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="AB14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="AD14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="AE14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="AF14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="AG14" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="BM11" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="BN11" s="3" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="12" spans="1:67" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+      <c r="AH14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="AI14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="AJ14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="AK14" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="AL14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="AM14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="AN14" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="AO14" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AP14" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AQ14" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AR14" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AS14" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="AT14" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="AU14" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV14" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AW14" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="AX14" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AY14" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="AZ14" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="BA14" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B12" s="1">
-        <v>0</v>
-      </c>
-      <c r="C12" s="1">
-        <v>0</v>
-      </c>
-      <c r="D12" s="1">
-        <v>0</v>
-      </c>
-      <c r="E12" s="1">
-        <v>0</v>
-      </c>
-      <c r="F12" s="1">
-        <v>0</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1">
-        <v>0</v>
-      </c>
-      <c r="O12" s="1">
-        <v>0</v>
-      </c>
-      <c r="P12" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>0</v>
-      </c>
-      <c r="R12" s="1">
-        <v>0</v>
-      </c>
-      <c r="S12" s="1">
-        <v>0</v>
-      </c>
-      <c r="T12" s="1">
-        <v>0</v>
-      </c>
-      <c r="U12" s="1">
-        <v>0</v>
-      </c>
-      <c r="V12" s="1">
-        <v>0</v>
-      </c>
-      <c r="W12" s="1">
-        <v>0</v>
-      </c>
-      <c r="X12" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="1">
-        <v>25</v>
-      </c>
-      <c r="Z12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AP12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="1">
-        <v>20</v>
-      </c>
-      <c r="AR12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AS12" s="1">
-        <v>10</v>
-      </c>
-      <c r="AT12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AU12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AV12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AW12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AX12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AZ12" s="1">
-        <v>0</v>
-      </c>
-      <c r="BA12" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB12" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC12" s="1">
-        <v>0</v>
-      </c>
-      <c r="BD12" s="1">
-        <v>0</v>
-      </c>
-      <c r="BE12" s="1">
-        <v>0</v>
-      </c>
-      <c r="BF12" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG12" s="1">
-        <v>0</v>
-      </c>
-      <c r="BH12" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI12" s="1">
-        <v>0</v>
-      </c>
-      <c r="BJ12" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK12" s="1">
-        <v>0</v>
-      </c>
-      <c r="BL12" s="1">
-        <v>0</v>
-      </c>
-      <c r="BM12" s="1">
-        <v>15</v>
-      </c>
-      <c r="BN12" s="1">
-        <v>10</v>
-      </c>
-      <c r="BO12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:67" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="V13" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="Y13" s="1"/>
-      <c r="AD13" s="1" t="s">
+      <c r="BB14" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="AF13"/>
-      <c r="AG13" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="AI13" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="AK13" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="AM13" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="AS13" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="BA13" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="BF13" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="BJ13" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="BK13" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="BM13" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="BN13" s="3" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="14" spans="1:67" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="V14" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="W14" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="X14" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="Y14" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="Z14" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="AA14" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="AB14" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="AC14" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="AD14" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="AF14" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="AG14" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="AH14" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="AI14" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="AJ14" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="AK14" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="AL14" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="AM14" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="AN14" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="AO14" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="AP14" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="AQ14" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="AR14" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="AS14" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="AT14" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="AU14" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="AV14" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="AW14" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="AX14" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="AY14" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="AZ14" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="BA14" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="BB14" s="3" t="s">
-        <v>226</v>
-      </c>
       <c r="BC14" s="3" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="BD14" s="3" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="BE14" s="3" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="BF14" s="3" t="s">
-        <v>226</v>
+        <v>321</v>
       </c>
       <c r="BG14" s="3" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="BH14" s="3" t="s">
-        <v>339</v>
+        <v>213</v>
       </c>
       <c r="BI14" s="3" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="BJ14" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="BK14" s="3" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="BL14" s="3" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="BM14" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="BN14" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="BO14" s="3" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Configs/EquipmentConfig.xlsx
+++ b/Assets/Resources/Configs/EquipmentConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProgram\SoulFighterSurvivor\Assets\Resources\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908AAA34-DA1C-4B04-92D1-A51F8B7346E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60FAD38A-EAB2-470E-99A3-7A90EDA4740E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="25845" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="377">
   <si>
     <t>id</t>
   </si>
@@ -1077,29 +1077,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>StatikkShiv</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>斯塔缇克电刃</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>连锁闪电</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"attackDamage":45,"attackSpeed":0.4,"percentageMovementSpeed":0.04}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>电火花</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hullbreaker</t>
-  </si>
-  <si>
     <t>海克斯注力刚壁</t>
   </si>
   <si>
@@ -1117,26 +1094,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>育恩塔尔荒野箭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击增幅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>YuentareWildArrow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"attackDamage":45,"attackSpeed":0.25}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>疾风骤雨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>TrinityForce</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1170,15 +1127,6 @@
   </si>
   <si>
     <t>你的盈能攻击附带&lt;color=#00D8FF&gt;100魔法伤害&lt;/color&gt;并提供持续1.5秒的45%&lt;sprite="Attributes" name="MovementSpeedIcon"&gt;。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击时，永久获得0.5%暴击几率，至多至25%。
-攻击敌人时，获得持续6秒的&lt;color=#E0C300&gt;30%&lt;sprite="Attributes" name="AttackSpeedIcon"&gt;&lt;/color&gt;。冷却时间30秒。攻击可以使冷却时间缩短1秒，根据暴击率有概率额外缩短1秒。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在施放你的终极技能后，获得持续8秒的&lt;color=#E0C300&gt;50%总&lt;sprite="Attributes" name="AttackSpeedIcon"&gt;&lt;/color&gt;和20%总&lt;sprite="Attributes" name="MovementSpeedIcon"&gt;。冷却时间10秒。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1323,10 +1271,6 @@
     <t>当你血量全满时，获得额外10%&lt;sprite="Attributes" name="AttackDamageIcon"&gt;。</t>
   </si>
   <si>
-    <t>你的下5次攻击会在命中时会触发连锁闪电，对最多5个目标造成&lt;color=#00D8FF&gt;{0:F0}=（80+45%&lt;sprite="Attributes" name="AttackDamageIcon"&gt;+&lt;color=#7700BB&gt;66%&lt;/color&gt;&lt;sprite="Attributes" name="AbilityPowerIcon"&gt;）的魔法伤害&lt;/color&gt;。冷却时间5秒。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>攻击造成30额外&lt;color=#00D8FF&gt;魔法伤害&lt;/color&gt;。每次攻击切换特效：附带光明的攻击提供8&lt;sprite="Attributes" name="AttackDefenseIcon"&gt;和&lt;sprite="Attributes" name="MagicDefenseIcon"&gt;；附带黑暗的攻击提供8%&lt;sprite="Attributes" name="AttackPenetrationIcon"&gt;和&lt;sprite="Attributes" name="MagicPenetrationIcon"&gt;。两种特效均持续5秒，最多叠加4层。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1355,52 +1299,40 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对英雄造成&lt;color=#FF6A6A&gt;物理伤害&lt;/color&gt;时会施加6%&lt;sprite="Attributes" name="AttackDefenseIcon"&gt;削减，持续6秒，至多叠至30%&lt;sprite="Attributes" name="AttackDefenseIcon"&gt;削减。
+    <t>狂怒切割</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fighter,Wizard,Assassin,Shooter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LegendaryFighterEquipmentAnvil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LegendaryShooterEquipmentAnvil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LegendaryAssassinEquipmentAnvil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对敌人造成&lt;color=#FF6A6A&gt;物理伤害&lt;/color&gt;时会施加6%&lt;sprite="Attributes" name="AttackDefenseIcon"&gt;削减，持续6秒，至多叠至30%&lt;sprite="Attributes" name="AttackDefenseIcon"&gt;削减。
 造成&lt;color=#FF6A6A&gt;物理伤害&lt;/color&gt;时会提供持续2秒的20&lt;sprite="Attributes" name="MovementSpeedIcon"&gt;。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>狂怒切割</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SunderedSky</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>焚天</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>持续作战</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"attackDamage": 40, "maxHealthPoint": 350, "abilityHaste": 10}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你对一个英雄打出的第一次攻击会暴击，并回复自身&lt;color=#0ACD02&gt;{0:F0}&lt;/color&gt; =（&lt;color=#FF6161&gt;150%基础&lt;sprite="Attributes" name="AttackDamageIcon"&gt;&lt;/color&gt;）外加&lt;color=#0ACD02&gt;6%已损失&lt;sprite="Attributes" name="MaxHealthPointIcon"&gt;&lt;/color&gt;。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>光盾打击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fighter,Wizard,Assassin,Shooter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LegendaryFighterEquipmentAnvil</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LegendaryShooterEquipmentAnvil</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LegendaryAssassinEquipmentAnvil</t>
+    <t>Shooter,Assassin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hullbreaker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在施放你的终极技能后，获得持续8秒的&lt;color=#E0C300&gt;50%总&lt;sprite="Attributes" name="AttackSpeedIcon"&gt;&lt;/color&gt;和20%&lt;sprite="Attributes" name="MovementSpeedIcon"&gt;。冷却时间10秒。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1750,14 +1682,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BN14"/>
+  <dimension ref="A1:BL14"/>
   <sheetFormatPr defaultColWidth="32.375" defaultRowHeight="18.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="24" width="32.375" style="1"/>
     <col min="26" max="16384" width="32.375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:66" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1783,13 +1715,13 @@
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>391</v>
+        <v>370</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>392</v>
+        <v>371</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>393</v>
+        <v>372</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>235</v>
@@ -1915,7 +1847,7 @@
         <v>291</v>
       </c>
       <c r="BA1" s="3" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="BB1" s="5" t="s">
         <v>297</v>
@@ -1926,38 +1858,30 @@
       <c r="BD1" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="BE1" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="BF1" s="3" t="s">
+      <c r="BE1" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="BF1" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="BG1" s="3" t="s">
-        <v>324</v>
+      <c r="BG1" s="5" t="s">
+        <v>327</v>
       </c>
       <c r="BH1" s="5" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="BI1" s="5" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="BJ1" s="5" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="BK1" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="BL1" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="BM1" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="BN1" s="3" t="s">
-        <v>384</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="BL1" s="3"/>
     </row>
-    <row r="2" spans="1:66" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>36</v>
       </c>
@@ -2115,7 +2039,7 @@
         <v>292</v>
       </c>
       <c r="BA2" s="3" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="BB2" s="5" t="s">
         <v>298</v>
@@ -2126,38 +2050,30 @@
       <c r="BD2" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="BE2" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="BF2" s="3" t="s">
+      <c r="BE2" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="BF2" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="BG2" s="3" t="s">
-        <v>322</v>
+      <c r="BG2" s="5" t="s">
+        <v>329</v>
       </c>
       <c r="BH2" s="5" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="BI2" s="5" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="BJ2" s="5" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="BK2" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="BL2" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="BM2" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="BN2" s="3" t="s">
-        <v>385</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="BL2" s="3"/>
     </row>
-    <row r="3" spans="1:66" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>78</v>
       </c>
@@ -2303,37 +2219,29 @@
         <v>307</v>
       </c>
       <c r="BE3" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="BF3" s="3" t="s">
         <v>318</v>
       </c>
       <c r="BG3" s="3" t="s">
-        <v>323</v>
+        <v>356</v>
       </c>
       <c r="BH3" s="3" t="s">
-        <v>329</v>
+        <v>273</v>
       </c>
       <c r="BI3" s="3" t="s">
-        <v>369</v>
+        <v>337</v>
       </c>
       <c r="BJ3" s="3" t="s">
-        <v>273</v>
+        <v>344</v>
       </c>
       <c r="BK3" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="BL3" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="BM3" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="BN3" s="3" t="s">
-        <v>386</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="BL3" s="3"/>
     </row>
-    <row r="4" spans="1:66" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>110</v>
       </c>
@@ -2523,17 +2431,8 @@
       <c r="BK4" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="BL4" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="BM4" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="BN4" s="1" t="s">
-        <v>113</v>
-      </c>
     </row>
-    <row r="5" spans="1:66" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>114</v>
       </c>
@@ -2723,17 +2622,8 @@
       <c r="BK5" s="1">
         <v>2500</v>
       </c>
-      <c r="BL5" s="1">
-        <v>2500</v>
-      </c>
-      <c r="BM5" s="1">
-        <v>2500</v>
-      </c>
-      <c r="BN5" s="1">
-        <v>2500</v>
-      </c>
     </row>
-    <row r="6" spans="1:66" ht="273" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:64" ht="273" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>115</v>
       </c>
@@ -2876,7 +2766,7 @@
         <v>294</v>
       </c>
       <c r="BA6" s="3" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="BB6" s="3" t="s">
         <v>300</v>
@@ -2888,42 +2778,34 @@
         <v>308</v>
       </c>
       <c r="BE6" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="BF6" s="3" t="s">
         <v>319</v>
       </c>
       <c r="BG6" s="3" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="BH6" s="3" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="BI6" s="3" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="BJ6" s="3" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="BK6" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="BL6" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="BM6" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="BN6" s="3" t="s">
-        <v>387</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="BL6" s="3"/>
     </row>
-    <row r="7" spans="1:66" ht="270" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:64" ht="270" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>146</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>147</v>
@@ -2978,7 +2860,7 @@
         <v>243</v>
       </c>
       <c r="AB7" s="3" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="AC7" s="1" t="s">
         <v>160</v>
@@ -3011,13 +2893,13 @@
         <v>166</v>
       </c>
       <c r="AN7" s="3" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="AO7" s="3" t="s">
         <v>261</v>
       </c>
       <c r="AP7" s="3" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="AQ7" s="3" t="s">
         <v>245</v>
@@ -3050,46 +2932,38 @@
         <v>296</v>
       </c>
       <c r="BA7" s="3" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="BB7" s="3" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="BC7" s="3" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="BE7" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="BF7" s="3" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="BG7" s="3" t="s">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="BH7" s="3" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="BI7" s="3" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="BJ7" s="3" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="BK7" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="BL7" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="BM7" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="BN7" s="3" t="s">
-        <v>388</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="BL7" s="3"/>
     </row>
-    <row r="8" spans="1:66" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:64" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>167</v>
       </c>
@@ -3223,7 +3097,7 @@
         <v>295</v>
       </c>
       <c r="BA8" s="3" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="BB8" s="3" t="s">
         <v>301</v>
@@ -3232,37 +3106,29 @@
         <v>305</v>
       </c>
       <c r="BE8" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="BF8" s="3" t="s">
         <v>320</v>
       </c>
       <c r="BG8" s="3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="BH8" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="BI8" s="3" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="BJ8" s="3" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="BK8" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="BL8" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="BM8" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="BN8" s="3" t="s">
-        <v>389</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="BL8" s="3"/>
     </row>
-    <row r="9" spans="1:66" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>196</v>
       </c>
@@ -3432,16 +3298,16 @@
         <v>0</v>
       </c>
       <c r="BE9" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BF9" s="1">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="BG9" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BH9" s="1">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BI9" s="1">
         <v>0</v>
@@ -3452,17 +3318,8 @@
       <c r="BK9" s="1">
         <v>0</v>
       </c>
-      <c r="BL9" s="1">
-        <v>0</v>
-      </c>
-      <c r="BM9" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN9" s="1">
-        <v>8</v>
-      </c>
     </row>
-    <row r="10" spans="1:66" ht="270.60000000000002" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:64" ht="270.60000000000002" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>197</v>
       </c>
@@ -3480,14 +3337,14 @@
       <c r="AQ10" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="BK10" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="BL10" s="3" t="s">
-        <v>377</v>
+      <c r="BI10" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="BJ10" s="3" t="s">
+        <v>363</v>
       </c>
     </row>
-    <row r="11" spans="1:66" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>200</v>
       </c>
@@ -3505,14 +3362,14 @@
       <c r="AQ11" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="BK11" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="BL11" s="3" t="s">
-        <v>359</v>
+      <c r="BI11" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="BJ11" s="3" t="s">
+        <v>346</v>
       </c>
     </row>
-    <row r="12" spans="1:66" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>205</v>
       </c>
@@ -3694,27 +3551,18 @@
         <v>0</v>
       </c>
       <c r="BI12" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BJ12" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BK12" s="1">
-        <v>15</v>
-      </c>
-      <c r="BL12" s="1">
-        <v>10</v>
-      </c>
-      <c r="BM12" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN12" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:66" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>206</v>
@@ -3761,34 +3609,34 @@
         <v>209</v>
       </c>
       <c r="AK13" s="3" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="AQ13" s="3" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="AY13" s="1" t="s">
         <v>207</v>
       </c>
       <c r="BA13" s="3" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="BD13" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="BH13" s="3" t="s">
-        <v>332</v>
+        <v>355</v>
+      </c>
+      <c r="BF13" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="BG13" s="3" t="s">
+        <v>354</v>
       </c>
       <c r="BI13" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="BK13" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="BL13" s="3" t="s">
-        <v>353</v>
+        <v>340</v>
+      </c>
+      <c r="BJ13" s="3" t="s">
+        <v>340</v>
       </c>
     </row>
-    <row r="14" spans="1:66" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>210</v>
       </c>
@@ -3811,7 +3659,7 @@
         <v>213</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>390</v>
+        <v>369</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>213</v>
@@ -3886,10 +3734,10 @@
         <v>211</v>
       </c>
       <c r="AG14" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="AH14" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="AI14" s="1" t="s">
         <v>211</v>
@@ -3955,38 +3803,30 @@
         <v>216</v>
       </c>
       <c r="BD14" s="3" t="s">
-        <v>216</v>
+        <v>374</v>
       </c>
       <c r="BE14" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="BF14" s="3" t="s">
-        <v>321</v>
+        <v>213</v>
       </c>
       <c r="BG14" s="3" t="s">
         <v>216</v>
       </c>
       <c r="BH14" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="BI14" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="BI14" s="3" t="s">
+      <c r="BJ14" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="BK14" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="BJ14" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="BK14" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="BL14" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="BM14" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="BN14" s="3" t="s">
-        <v>213</v>
-      </c>
+      <c r="BL14" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/Resources/Configs/EquipmentConfig.xlsx
+++ b/Assets/Resources/Configs/EquipmentConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProgram\SoulFighterSurvivor\Assets\Resources\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60FAD38A-EAB2-470E-99A3-7A90EDA4740E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62BC05D3-C0A8-445F-85FF-719207A84C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="25845" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="377">
   <si>
     <t>id</t>
   </si>
@@ -1299,10 +1299,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>狂怒切割</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Fighter,Wizard,Assassin,Shooter</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1319,11 +1315,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对敌人造成&lt;color=#FF6A6A&gt;物理伤害&lt;/color&gt;时会施加6%&lt;sprite="Attributes" name="AttackDefenseIcon"&gt;削减，持续6秒，至多叠至30%&lt;sprite="Attributes" name="AttackDefenseIcon"&gt;削减。
-造成&lt;color=#FF6A6A&gt;物理伤害&lt;/color&gt;时会提供持续2秒的20&lt;sprite="Attributes" name="MovementSpeedIcon"&gt;。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Shooter,Assassin</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1333,6 +1324,14 @@
   </si>
   <si>
     <t>在施放你的终极技能后，获得持续8秒的&lt;color=#E0C300&gt;50%总&lt;sprite="Attributes" name="AttackSpeedIcon"&gt;&lt;/color&gt;和20%&lt;sprite="Attributes" name="MovementSpeedIcon"&gt;。冷却时间10秒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>切割</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对敌人造成&lt;color=#FF6A6A&gt;伤害&lt;/color&gt;时会施加6%&lt;sprite="Attributes" name="AttackDefenseIcon"&gt;削减，持续6秒，至多叠至30%&lt;sprite="Attributes" name="AttackDefenseIcon"&gt;削减。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1715,13 +1714,13 @@
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>371</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>372</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>235</v>
@@ -1846,7 +1845,7 @@
       <c r="AZ1" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="BA1" s="3" t="s">
+      <c r="BA1" s="5" t="s">
         <v>365</v>
       </c>
       <c r="BB1" s="5" t="s">
@@ -1859,7 +1858,7 @@
         <v>310</v>
       </c>
       <c r="BE1" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="BF1" s="5" t="s">
         <v>316</v>
@@ -2038,7 +2037,7 @@
       <c r="AZ2" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="BA2" s="3" t="s">
+      <c r="BA2" s="5" t="s">
         <v>366</v>
       </c>
       <c r="BB2" s="5" t="s">
@@ -2932,7 +2931,7 @@
         <v>296</v>
       </c>
       <c r="BA7" s="3" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="BB7" s="3" t="s">
         <v>324</v>
@@ -2941,7 +2940,7 @@
         <v>323</v>
       </c>
       <c r="BE7" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="BF7" s="3" t="s">
         <v>326</v>
@@ -3097,7 +3096,7 @@
         <v>295</v>
       </c>
       <c r="BA8" s="3" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="BB8" s="3" t="s">
         <v>301</v>
@@ -3659,7 +3658,7 @@
         <v>213</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>213</v>
@@ -3803,7 +3802,7 @@
         <v>216</v>
       </c>
       <c r="BD14" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="BE14" s="3" t="s">
         <v>213</v>

--- a/Assets/Resources/Configs/EquipmentConfig.xlsx
+++ b/Assets/Resources/Configs/EquipmentConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProgram\SoulFighterSurvivor\Assets\Resources\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62BC05D3-C0A8-445F-85FF-719207A84C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{664BEAC6-4F33-48AD-9BA0-EE34DBD2C730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="25845" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="381">
   <si>
     <t>id</t>
   </si>
@@ -1332,6 +1332,22 @@
   </si>
   <si>
     <t>对敌人造成&lt;color=#FF6A6A&gt;伤害&lt;/color&gt;时会施加6%&lt;sprite="Attributes" name="AttackDefenseIcon"&gt;削减，持续6秒，至多叠至30%&lt;sprite="Attributes" name="AttackDefenseIcon"&gt;削减。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金铲铲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GoldenShovel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火力全开！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"attackDamage": 70, "abilityPower": 120, "attackSpeed": 0.5, "criticalRate": 0.5, "maxHealthPoint": 250, "attackDefense": 30, "magicDefense": 30, "maxMagicPoint": 250, "abilityHaste": 20, "percentageMovementSpeed": 0.1, "lifeSteal": 0.1}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1878,7 +1894,9 @@
       <c r="BK1" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="BL1" s="3"/>
+      <c r="BL1" s="5" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="2" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -2070,7 +2088,9 @@
       <c r="BK2" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="BL2" s="3"/>
+      <c r="BL2" s="5" t="s">
+        <v>377</v>
+      </c>
     </row>
     <row r="3" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -2238,7 +2258,9 @@
       <c r="BK3" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="BL3" s="3"/>
+      <c r="BL3" s="3" t="s">
+        <v>379</v>
+      </c>
     </row>
     <row r="4" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2430,6 +2452,9 @@
       <c r="BK4" s="1" t="s">
         <v>113</v>
       </c>
+      <c r="BL4" s="3" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="5" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -2621,6 +2646,9 @@
       <c r="BK5" s="1">
         <v>2500</v>
       </c>
+      <c r="BL5" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:64" ht="273" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -2797,7 +2825,9 @@
       <c r="BK6" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="BL6" s="3"/>
+      <c r="BL6" s="3" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="7" spans="1:64" ht="270" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
@@ -3317,6 +3347,9 @@
       <c r="BK9" s="1">
         <v>0</v>
       </c>
+      <c r="BL9" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:64" ht="270.60000000000002" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
@@ -3558,6 +3591,9 @@
       <c r="BK12" s="1">
         <v>0</v>
       </c>
+      <c r="BL12" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
@@ -3825,7 +3861,9 @@
       <c r="BK14" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="BL14" s="3"/>
+      <c r="BL14" s="3" t="s">
+        <v>368</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/Resources/Configs/EquipmentConfig.xlsx
+++ b/Assets/Resources/Configs/EquipmentConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProgram\SoulFighterSurvivor\Assets\Resources\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{664BEAC6-4F33-48AD-9BA0-EE34DBD2C730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34EB7F03-19FE-4849-BB9E-7550EDC5E4EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="25845" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="387">
   <si>
     <t>id</t>
   </si>
@@ -1348,6 +1348,30 @@
   </si>
   <si>
     <t>{"attackDamage": 70, "abilityPower": 120, "attackSpeed": 0.5, "criticalRate": 0.5, "maxHealthPoint": 250, "attackDefense": 30, "magicDefense": 30, "maxMagicPoint": 250, "abilityHaste": 20, "percentageMovementSpeed": 0.1, "lifeSteal": 0.1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你是黄金奖杯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GoldTrophy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结束了？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"attackDamage": 114, "abilityPower": 514, "attackSpeed": 3.5, "criticalRate": 2.34}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>购买时获得胜利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>证明</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1697,14 +1721,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BL14"/>
+  <dimension ref="A1:BM14"/>
   <sheetFormatPr defaultColWidth="32.375" defaultRowHeight="18.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="24" width="32.375" style="1"/>
     <col min="26" max="16384" width="32.375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:65" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1897,8 +1921,11 @@
       <c r="BL1" s="5" t="s">
         <v>378</v>
       </c>
+      <c r="BM1" s="5" t="s">
+        <v>382</v>
+      </c>
     </row>
-    <row r="2" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:65" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>36</v>
       </c>
@@ -2091,8 +2118,11 @@
       <c r="BL2" s="5" t="s">
         <v>377</v>
       </c>
+      <c r="BM2" s="5" t="s">
+        <v>381</v>
+      </c>
     </row>
-    <row r="3" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:65" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>78</v>
       </c>
@@ -2261,8 +2291,11 @@
       <c r="BL3" s="3" t="s">
         <v>379</v>
       </c>
+      <c r="BM3" s="3" t="s">
+        <v>383</v>
+      </c>
     </row>
-    <row r="4" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:65" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>110</v>
       </c>
@@ -2455,8 +2488,11 @@
       <c r="BL4" s="3" t="s">
         <v>280</v>
       </c>
+      <c r="BM4" s="1" t="s">
+        <v>112</v>
+      </c>
     </row>
-    <row r="5" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:65" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>114</v>
       </c>
@@ -2649,8 +2685,11 @@
       <c r="BL5" s="1">
         <v>0</v>
       </c>
+      <c r="BM5" s="1">
+        <v>18888</v>
+      </c>
     </row>
-    <row r="6" spans="1:64" ht="273" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:65" ht="273" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>115</v>
       </c>
@@ -2828,8 +2867,11 @@
       <c r="BL6" s="3" t="s">
         <v>380</v>
       </c>
+      <c r="BM6" s="3" t="s">
+        <v>384</v>
+      </c>
     </row>
-    <row r="7" spans="1:64" ht="270" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:65" ht="270" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>146</v>
       </c>
@@ -2991,8 +3033,11 @@
         <v>360</v>
       </c>
       <c r="BL7" s="3"/>
+      <c r="BM7" s="3" t="s">
+        <v>385</v>
+      </c>
     </row>
-    <row r="8" spans="1:64" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:65" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>167</v>
       </c>
@@ -3156,8 +3201,11 @@
         <v>351</v>
       </c>
       <c r="BL8" s="3"/>
+      <c r="BM8" s="3" t="s">
+        <v>386</v>
+      </c>
     </row>
-    <row r="9" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:65" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>196</v>
       </c>
@@ -3350,8 +3398,11 @@
       <c r="BL9" s="1">
         <v>0</v>
       </c>
+      <c r="BM9" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:64" ht="270.60000000000002" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:65" ht="270.60000000000002" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>197</v>
       </c>
@@ -3376,7 +3427,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="11" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:65" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>200</v>
       </c>
@@ -3401,7 +3452,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="12" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:65" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>205</v>
       </c>
@@ -3594,8 +3645,11 @@
       <c r="BL12" s="1">
         <v>0</v>
       </c>
+      <c r="BM12" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:65" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>353</v>
       </c>
@@ -3671,7 +3725,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="14" spans="1:64" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:65" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>210</v>
       </c>
@@ -3862,6 +3916,9 @@
         <v>216</v>
       </c>
       <c r="BL14" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="BM14" s="3" t="s">
         <v>368</v>
       </c>
     </row>

--- a/Assets/Resources/Configs/EquipmentConfig.xlsx
+++ b/Assets/Resources/Configs/EquipmentConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProgram\SoulFighterSurvivor\Assets\Resources\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34EB7F03-19FE-4849-BB9E-7550EDC5E4EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E099D88-2F71-4F7A-873D-B74BD504EED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="25845" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2686,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="BM5" s="1">
-        <v>18888</v>
+        <v>8888</v>
       </c>
     </row>
     <row r="6" spans="1:65" ht="273" customHeight="1" x14ac:dyDescent="0.2">

--- a/Assets/Resources/Configs/EquipmentConfig.xlsx
+++ b/Assets/Resources/Configs/EquipmentConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProgram\SoulFighterSurvivor\Assets\Resources\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E099D88-2F71-4F7A-873D-B74BD504EED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E5789D-F44C-4AF2-9443-18B65C70AB86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="25845" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2488,8 +2488,8 @@
       <c r="BL4" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="BM4" s="1" t="s">
-        <v>112</v>
+      <c r="BM4" s="3" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:65" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
